--- a/音节表.xlsx
+++ b/音节表.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/16f5f3de81894523/Yime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{353AEFBD-68D8-4D4D-B6FF-3D08F9BEC46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF6123B-E630-4D6C-BAD7-4A8921D9EDB8}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{353AEFBD-68D8-4D4D-B6FF-3D08F9BEC46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04D5C289-99A6-44F4-A199-75B0A6634F73}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{72E103A0-AF67-473E-9619-FEBDFB20CF8E}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="3" xr2:uid="{72E103A0-AF67-473E-9619-FEBDFB20CF8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="173">
   <si>
     <t>高调阴平</t>
   </si>
@@ -267,6 +270,294 @@
   </si>
   <si>
     <t>󰀇</t>
+  </si>
+  <si>
+    <t>音元</t>
+  </si>
+  <si>
+    <t>片音</t>
+  </si>
+  <si>
+    <t>分布条件</t>
+  </si>
+  <si>
+    <t>󰃼</t>
+  </si>
+  <si>
+    <t>[󰍒]</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}_󰃼󰃼，{󰃐，󰃑，󰃒，󰃓}_󰃽󰃾，_󰃼󰃳，_󰃽󰃵；</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}󰃼_󰃼，󰃳_󰃼，󰃼_󰃳，󰃰_󰃳</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}󰃼󰃼_，󰃳󰃼_，󰃾󰃽_，{󰃐，󰃑，󰃒，󰃓}󰃾󰃽_，󰃤󰃵󰃽_</t>
+  </si>
+  <si>
+    <t>[󰍗]</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}_󰃼󰃼，{-{󰃐，󰃑，󰃒，󰃓}}_󰃽󰃾，_󰃼󰄋；</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}󰃼_󰃼；󰃼_󰄋，󰃰_󰄋，󰃳_󰄋，󰃶_󰄋</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}󰃼󰃼_，{-{󰃐，󰃑，󰃒，󰃓}}󰃾󰃽_，󰃐_󰃽󰄍</t>
+  </si>
+  <si>
+    <t>󰃽</t>
+  </si>
+  <si>
+    <t>[󰍓]</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}󰃾_󰃼，󰃤󰃵_󰃼，{󰃐，󰃑，󰃒，󰃓}󰃼_󰃾，󰃳_󰃾，</t>
+  </si>
+  <si>
+    <t>󰃤󰃾_󰃳，󰃲_󰃳，󰃼_󰃵，󰃰_󰃵</t>
+  </si>
+  <si>
+    <t>[󰍘]</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}󰃾_󰃼，{-{󰃐，󰃑，󰃒，󰃓}}󰃼_󰃾</t>
+  </si>
+  <si>
+    <t>󰃤󰃾_󰄋，󰃲_󰄋，󰃵_󰄋，󰃸_󰄋，󰃤󰃼_󰄍，󰃰_󰄍，󰃳_󰄍，󰃶_󰄍</t>
+  </si>
+  <si>
+    <t>󰃾</t>
+  </si>
+  <si>
+    <t>[󰍔]</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}_󰃽󰃼，󰃤_󰃽󰃳</t>
+  </si>
+  <si>
+    <t>[󰍙]</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}_󰃽󰃼，󰃤_󰃽󰄋</t>
+  </si>
+  <si>
+    <t>[󰍕]</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}_󰃾󰃾，_󰃾󰃵</t>
+  </si>
+  <si>
+    <t>[󰍚]</t>
+  </si>
+  <si>
+    <t>{-{󰃐，󰃑，󰃒，󰃓}}_󰃾󰃾，󰃑_󰃾󰄍</t>
+  </si>
+  <si>
+    <t>[󰍖]</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}󰃾_󰃾，󰃾_󰃵，󰃲_󰃵；{󰃐，󰃑，󰃒，󰃓}󰃾󰃾_，</t>
+  </si>
+  <si>
+    <t>{󰃐，󰃑，󰃒，󰃓}󰃼󰃽_，󰃳󰃽_</t>
+  </si>
+  <si>
+    <t>[󰍛]</t>
+  </si>
+  <si>
+    <t>󰃾_󰃾；󰃾󰃾_，󰃼󰃽_；󰃙󰃾_󰄍，󰃲_󰄍，󰃵_󰄍，󰃸_󰄍</t>
+  </si>
+  <si>
+    <t>󰃳</t>
+  </si>
+  <si>
+    <t>[󰌪]</t>
+  </si>
+  <si>
+    <t>_󰃳󰃳，_󰃴󰃵，󰃳_󰃳，󰃳󰃳_，󰃵󰃴_；_󰃹󰃹，_󰃼󰃼，_󰃹󰃰，_󰃿󰃰，_󰃹󰄈，_󰃿󰄈，_󰃹󰄋，_󰃼󰄋；_󰃺󰃻，_󰃽󰃾，_󰃺󰃲，_󰄀󰃲，_󰃺󰄊，_󰄀󰄊，_󰃺󰄍，_󰃽󰄍</t>
+  </si>
+  <si>
+    <t>[󰌯]</t>
+  </si>
+  <si>
+    <t>󰃹󰃹_，󰃼󰃼_，󰃰󰃹_，󰃰󰃼_，󰃻󰃺_，󰃾󰃽_，󰃲󰃺_，󰃲󰃽_</t>
+  </si>
+  <si>
+    <t>󰃴</t>
+  </si>
+  <si>
+    <t>[󰌫]</t>
+  </si>
+  <si>
+    <t>󰃵_󰃳，󰃳_󰃵</t>
+  </si>
+  <si>
+    <t>[󰌰]</t>
+  </si>
+  <si>
+    <t>󰃻󰃻_，󰃲󰃻_，󰃾󰃾_，󰃲_</t>
+  </si>
+  <si>
+    <t>󰃵</t>
+  </si>
+  <si>
+    <t>[󰌬]</t>
+  </si>
+  <si>
+    <t>_󰃴󰃳，_󰃺󰃹，_󰃽󰃼，_󰃺󰃰，_󰄀󰃰，_󰃺󰄈，_󰄀󰄈，_󰃺󰄋，_󰃽󰄋</t>
+  </si>
+  <si>
+    <t>[󰌱]</t>
+  </si>
+  <si>
+    <t>󰃹󰃺_，󰃰󰃺_，󰃼󰃽_，󰃰󰃽_</t>
+  </si>
+  <si>
+    <t>[󰌭]</t>
+  </si>
+  <si>
+    <t>_󰃵󰃵，_󰃻󰃻，_󰃾󰃾，_󰃻󰃲，_󰄁󰃲，_󰃻󰄊，_󰄁󰄊，_󰃻󰄍，_󰃾󰄍</t>
+  </si>
+  <si>
+    <t>[󰌮]</t>
+  </si>
+  <si>
+    <t>󰃵_󰃵，󰃵_，󰃳󰃴_</t>
+  </si>
+  <si>
+    <t>[󰌳]</t>
+  </si>
+  <si>
+    <t>󰃹</t>
+  </si>
+  <si>
+    <t>[󰌾]</t>
+  </si>
+  <si>
+    <t>_󰃹󰃹，_󰃺󰃻；󰃹_󰃹，󰃰_󰃹，󰃳_󰃹；󰃹󰃹_，󰃰󰃹_，󰃳󰃹_；󰃻󰃺_，󰃲󰃺_，󰃵󰃺_</t>
+  </si>
+  <si>
+    <t>[󰍃]</t>
+  </si>
+  <si>
+    <t>_󰃹󰄈，_󰃺󰄊；󰃹_󰄈，󰃳_󰄈</t>
+  </si>
+  <si>
+    <t>[󰍍]</t>
+  </si>
+  <si>
+    <t>_󰃹󰃳，_󰃹󰄋；_󰃺󰃵，_󰃺󰄍；󰃹_󰃳，󰃰_󰃳；󰃹_󰄋，󰃰_󰄋，󰃳_󰄋</t>
+  </si>
+  <si>
+    <t>[󰍈]</t>
+  </si>
+  <si>
+    <t>_󰃹󰃰，_󰃺󰃲；󰃹_󰃰，󰃳_󰃰；󰃰_󰄈，󰃶_󰄈</t>
+  </si>
+  <si>
+    <t>󰃺</t>
+  </si>
+  <si>
+    <t>[󰌿]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃹，󰃲_󰃹，󰃵_󰃹；󰃹_󰃻，󰃰_󰃻，󰃳_󰃻</t>
+  </si>
+  <si>
+    <t>[󰍄]</t>
+  </si>
+  <si>
+    <t>󰃻_󰄈，󰃵_󰄈，󰃹_󰄊，󰃳_󰄊</t>
+  </si>
+  <si>
+    <t>[󰍎]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃳，󰃻_󰄋，󰃲_󰃳，󰃲_󰄋，󰃵_󰄋，󰃹_󰃵，󰃹_󰄍，󰃰_󰃵，󰃰_󰄍，󰃳_󰄍，</t>
+  </si>
+  <si>
+    <t>[󰍉]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃰，󰃤󰃵_󰃰，󰃹_󰃲，󰃳_󰃲；󰃲_󰄈，󰃸_󰄈，󰃰_󰄊，󰃶_󰄊</t>
+  </si>
+  <si>
+    <t>󰃻</t>
+  </si>
+  <si>
+    <t>[󰍀]</t>
+  </si>
+  <si>
+    <t>_󰃺󰃹</t>
+  </si>
+  <si>
+    <t>[󰍅]</t>
+  </si>
+  <si>
+    <t>_󰃺󰄈</t>
+  </si>
+  <si>
+    <t>[󰍏]</t>
+  </si>
+  <si>
+    <t>_󰃺󰃳，_󰃺󰄋</t>
+  </si>
+  <si>
+    <t>[󰍊]</t>
+  </si>
+  <si>
+    <t>_󰃺󰃰</t>
+  </si>
+  <si>
+    <t>[󰍁]</t>
+  </si>
+  <si>
+    <t>_󰃻󰃻</t>
+  </si>
+  <si>
+    <t>[󰍆]</t>
+  </si>
+  <si>
+    <t>_󰃻󰄊</t>
+  </si>
+  <si>
+    <t>[󰍐]</t>
+  </si>
+  <si>
+    <t>_󰃻󰃵，󰃒_󰃻󰄍</t>
+  </si>
+  <si>
+    <t>[󰍋]</t>
+  </si>
+  <si>
+    <t>_󰃻󰃲</t>
+  </si>
+  <si>
+    <t>[󰍂]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃻，󰃲_󰃻，󰃵_󰃻；󰃻󰃻_，󰃲󰃻_，󰃵󰃻_，󰃹󰃺_，󰃰󰃺_，󰃳󰃺_</t>
+  </si>
+  <si>
+    <t>[󰍇]</t>
+  </si>
+  <si>
+    <t>󰃻_󰄊，󰃵_󰄊</t>
+  </si>
+  <si>
+    <t>[󰍑]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃵，󰃲_󰃵，󰃒󰃻_󰄍，󰃲_󰄍，󰃵_󰄍</t>
+  </si>
+  <si>
+    <t>[󰍌]</t>
+  </si>
+  <si>
+    <t>󰃻_󰃲，󰃵_󰃲，󰃲_󰄊，󰃸_󰄊</t>
   </si>
 </sst>
 </file>
@@ -305,7 +596,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -365,18 +656,91 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -389,6 +753,39 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -405,6 +802,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -728,657 +1129,657 @@
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1" t="s">
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1" t="s">
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1" t="s">
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
+      <c r="N1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
+      <c r="O1" s="5"/>
+      <c r="P1" s="5"/>
+      <c r="Q1" s="5"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A2" s="4"/>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="3"/>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="J2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="K2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="L2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="N2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="O2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="P2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A3" s="5"/>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="4"/>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2" t="s">
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
+      <c r="H3" s="1"/>
+      <c r="I3" s="1"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2" t="s">
+      <c r="L3" s="1"/>
+      <c r="M3" s="1"/>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
+      <c r="P3" s="1"/>
+      <c r="Q3" s="1"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+      <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="1"/>
+      <c r="C4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2" t="s">
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
+      <c r="H4" s="1"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2" t="s">
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
+      <c r="P4" s="1"/>
+      <c r="Q4" s="1"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2" t="s">
+      <c r="B5" s="1"/>
+      <c r="C5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2" t="s">
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2" t="s">
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
+      <c r="P5" s="1"/>
+      <c r="Q5" s="1"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2" t="s">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2" t="s">
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="N7" s="1"/>
+      <c r="O7" s="1"/>
+      <c r="P7" s="1"/>
+      <c r="Q7" s="1"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2" t="s">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2" t="s">
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2" t="s">
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2" t="s">
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="N8" s="1"/>
+      <c r="O8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
+      <c r="P8" s="1"/>
+      <c r="Q8" s="1"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2" t="s">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2" t="s">
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2" t="s">
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
+      <c r="N9" s="1"/>
+      <c r="O9" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
+      <c r="P9" s="1"/>
+      <c r="Q9" s="1"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
+      <c r="A10" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2" t="s">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2" t="s">
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2" t="s">
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2" t="s">
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
+      <c r="N10" s="1"/>
+      <c r="O10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
+      <c r="P10" s="1"/>
+      <c r="Q10" s="1"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
+      <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2" t="s">
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2" t="s">
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
+      <c r="N11" s="1"/>
+      <c r="O11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="P11" s="1"/>
+      <c r="Q11" s="1"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
+      <c r="A12" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2" t="s">
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2" t="s">
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A13" s="2" t="s">
+      <c r="A13" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A14" s="2" t="s">
+      <c r="A14" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A15" s="2" t="s">
+      <c r="A15" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A16" s="2" t="s">
+      <c r="A16" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B16" s="2"/>
-      <c r="C16" s="2" t="s">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2" t="s">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2" t="s">
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A17" s="2" t="s">
+      <c r="A17" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B17" s="2"/>
-      <c r="C17" s="2" t="s">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2" t="s">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2" t="s">
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
+      <c r="A18" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2" t="s">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2" t="s">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2" t="s">
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
+      <c r="A19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B19" s="2"/>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
+      <c r="A20" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+      <c r="K20" s="1"/>
+      <c r="L20" s="1"/>
+      <c r="M20" s="1"/>
+      <c r="N20" s="1"/>
+      <c r="O20" s="1"/>
+      <c r="P20" s="1"/>
+      <c r="Q20" s="1"/>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A21" s="2" t="s">
+      <c r="A21" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="2"/>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+      <c r="K21" s="1"/>
+      <c r="L21" s="1"/>
+      <c r="M21" s="1"/>
+      <c r="N21" s="1"/>
+      <c r="O21" s="1"/>
+      <c r="P21" s="1"/>
+      <c r="Q21" s="1"/>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+      <c r="K22" s="1"/>
+      <c r="L22" s="1"/>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+      <c r="O22" s="1"/>
+      <c r="P22" s="1"/>
+      <c r="Q22" s="1"/>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B23" s="2"/>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+      <c r="K23" s="1"/>
+      <c r="L23" s="1"/>
+      <c r="M23" s="1"/>
+      <c r="N23" s="1"/>
+      <c r="O23" s="1"/>
+      <c r="P23" s="1"/>
+      <c r="Q23" s="1"/>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A24" s="2" t="s">
+      <c r="A24" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+      <c r="K24" s="1"/>
+      <c r="L24" s="1"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+      <c r="O24" s="1"/>
+      <c r="P24" s="1"/>
+      <c r="Q24" s="1"/>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B25" s="2"/>
-      <c r="C25" s="2"/>
-      <c r="D25" s="2"/>
-      <c r="E25" s="2"/>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="2"/>
-      <c r="M25" s="2"/>
-      <c r="N25" s="2"/>
-      <c r="O25" s="2"/>
-      <c r="P25" s="2"/>
-      <c r="Q25" s="2"/>
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+      <c r="K25" s="1"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -1391,4 +1792,522 @@
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FEB58A5-1728-4079-BB55-9328B179A951}">
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="14"/>
+      <c r="C3" s="15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="14" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="14"/>
+      <c r="B6" s="14"/>
+      <c r="C6" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="14"/>
+      <c r="C7" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="14"/>
+      <c r="C9" s="15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="14"/>
+      <c r="B13" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="14"/>
+      <c r="B14" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="14"/>
+      <c r="B15" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="14"/>
+      <c r="B16" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A18" s="14"/>
+      <c r="B18" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>109</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A12:A18"/>
+    <mergeCell ref="B16:B17"/>
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="A8:A11"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B10:B11"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E416BD9-D5C8-46E3-80E3-25FB2B5EEC4B}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="94.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="14"/>
+      <c r="B3" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="14"/>
+      <c r="B5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="14" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="14"/>
+      <c r="B7" s="13" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="14"/>
+      <c r="B8" s="13" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="14"/>
+      <c r="B9" s="13" t="s">
+        <v>127</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="14"/>
+      <c r="B10" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A6:A10"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A3F904-AA6C-4775-9145-5EFA27CD8A5E}">
+  <dimension ref="A1:C21"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="2" width="4.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="49.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="10"/>
+      <c r="B3" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="10"/>
+      <c r="B4" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="12"/>
+      <c r="B5" s="9" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9" t="s">
+        <v>142</v>
+      </c>
+      <c r="C7" s="8" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9" t="s">
+        <v>144</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="12"/>
+      <c r="B9" s="9" t="s">
+        <v>146</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="10"/>
+      <c r="B11" s="9" t="s">
+        <v>151</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="10"/>
+      <c r="B12" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="C12" s="8" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="10"/>
+      <c r="B13" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="10"/>
+      <c r="B14" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="8" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="10"/>
+      <c r="B15" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="8" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="10"/>
+      <c r="B16" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="10"/>
+      <c r="B17" s="9" t="s">
+        <v>163</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="10"/>
+      <c r="B18" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="10"/>
+      <c r="B19" s="9" t="s">
+        <v>167</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="10"/>
+      <c r="B20" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="12"/>
+      <c r="B21" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>172</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A21"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/音节表.xlsx
+++ b/音节表.xlsx
@@ -8,15 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/16f5f3de81894523/Yime/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="42" documentId="8_{353AEFBD-68D8-4D4D-B6FF-3D08F9BEC46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{04D5C289-99A6-44F4-A199-75B0A6634F73}"/>
+  <xr:revisionPtr revIDLastSave="88" documentId="8_{353AEFBD-68D8-4D4D-B6FF-3D08F9BEC46B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D867452E-1787-49C1-B32B-0D813B1718D5}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="3" xr2:uid="{72E103A0-AF67-473E-9619-FEBDFB20CF8E}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="25780" windowHeight="20970" activeTab="5" xr2:uid="{72E103A0-AF67-473E-9619-FEBDFB20CF8E}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
     <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="218">
   <si>
     <t>高调阴平</t>
   </si>
@@ -558,6 +560,148 @@
   </si>
   <si>
     <t>󰃻_󰃲，󰃵_󰃲，󰃲_󰄊，󰃸_󰄊</t>
+  </si>
+  <si>
+    <t>i</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>ʏ</t>
+  </si>
+  <si>
+    <t>ᴀ</t>
+  </si>
+  <si>
+    <t>o</t>
+  </si>
+  <si>
+    <t>ᴇ</t>
+  </si>
+  <si>
+    <t>󰉺</t>
+  </si>
+  <si>
+    <t>󰉻</t>
+  </si>
+  <si>
+    <t>n</t>
+  </si>
+  <si>
+    <t>ŋ</t>
+  </si>
+  <si>
+    <t>ᴀi</t>
+  </si>
+  <si>
+    <t>ᴇi</t>
+  </si>
+  <si>
+    <t>ᴀu</t>
+  </si>
+  <si>
+    <t>ou</t>
+  </si>
+  <si>
+    <t>ᴀn</t>
+  </si>
+  <si>
+    <t>ᴇn</t>
+  </si>
+  <si>
+    <t>ᴀŋ</t>
+  </si>
+  <si>
+    <t>oŋ</t>
+  </si>
+  <si>
+    <t>iᴀ</t>
+  </si>
+  <si>
+    <t>iᴇ</t>
+  </si>
+  <si>
+    <t>uᴀ</t>
+  </si>
+  <si>
+    <t>uo</t>
+  </si>
+  <si>
+    <t>ʏᴇ</t>
+  </si>
+  <si>
+    <t>iᴀu</t>
+  </si>
+  <si>
+    <t>iou</t>
+  </si>
+  <si>
+    <t>iᴀn</t>
+  </si>
+  <si>
+    <t>iᴇn</t>
+  </si>
+  <si>
+    <t>iᴀŋ</t>
+  </si>
+  <si>
+    <t>ioŋ</t>
+  </si>
+  <si>
+    <t>uᴀi</t>
+  </si>
+  <si>
+    <t>uᴇi</t>
+  </si>
+  <si>
+    <t>uᴀn</t>
+  </si>
+  <si>
+    <t>uᴇn</t>
+  </si>
+  <si>
+    <t>uᴀŋ</t>
+  </si>
+  <si>
+    <t>uoŋ</t>
+  </si>
+  <si>
+    <t>ʏᴀn</t>
+  </si>
+  <si>
+    <t>ʏᴇn</t>
+  </si>
+  <si>
+    <t>ʏoŋ</t>
+  </si>
+  <si>
+    <t>无尾韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有尾韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>无头韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有头韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>噫头韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>呜头韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>吁头韵母</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -596,7 +740,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -732,13 +876,42 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -786,6 +959,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2309,5 +2506,493 @@
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90CD073-5505-4BDB-8E81-A8D2A0379EFE}">
+  <dimension ref="A1:T5"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="1.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="2.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="2.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="1.9140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="2.08203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.33203125" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="3.5" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="3.9140625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="3.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A1" s="16"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="17" t="s">
+        <v>211</v>
+      </c>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
+      <c r="L1" s="18"/>
+      <c r="M1" s="18" t="s">
+        <v>212</v>
+      </c>
+      <c r="N1" s="18"/>
+      <c r="O1" s="18"/>
+      <c r="P1" s="18"/>
+      <c r="Q1" s="18"/>
+      <c r="R1" s="18"/>
+      <c r="S1" s="18"/>
+      <c r="T1" s="18"/>
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A2" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="21"/>
+      <c r="C2" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="F2" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="I2" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="J2" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="K2" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="L2" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="M2" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="N2" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="O2" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="P2" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q2" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="R2" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="S2" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="T2" s="13" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A3" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="P3" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="Q3" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="R3" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="S3" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="T3" s="13" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A4" s="19"/>
+      <c r="B4" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="N4" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="R4" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="S4" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="T4" s="13" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="A5" s="19"/>
+      <c r="B5" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
+      <c r="H5" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="I5" s="13"/>
+      <c r="J5" s="13"/>
+      <c r="K5" s="13"/>
+      <c r="L5" s="13"/>
+      <c r="M5" s="13"/>
+      <c r="N5" s="13"/>
+      <c r="O5" s="13"/>
+      <c r="P5" s="13"/>
+      <c r="Q5" s="13" t="s">
+        <v>208</v>
+      </c>
+      <c r="R5" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="S5" s="13"/>
+      <c r="T5" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C1:L1"/>
+    <mergeCell ref="M1:T1"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B29752CE-A6DC-4EE5-BFFC-1CCCD9480FC0}">
+  <dimension ref="A1:E20"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="2.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="22"/>
+      <c r="B1" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>214</v>
+      </c>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="22"/>
+      <c r="B2" s="14"/>
+      <c r="C2" s="13" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="13" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="23"/>
+      <c r="B4" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="23"/>
+      <c r="B5" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="23"/>
+      <c r="B6" s="13" t="s">
+        <v>176</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="13"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="23"/>
+      <c r="B7" s="13" t="s">
+        <v>177</v>
+      </c>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="E7" s="13"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="23"/>
+      <c r="B8" s="13" t="s">
+        <v>178</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="23"/>
+      <c r="B9" s="13" t="s">
+        <v>179</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="13"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="23"/>
+      <c r="B10" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C10" s="13"/>
+      <c r="D10" s="13"/>
+      <c r="E10" s="13"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="23"/>
+      <c r="B11" s="13" t="s">
+        <v>181</v>
+      </c>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="23"/>
+      <c r="B12" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="B13" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="C13" s="13"/>
+      <c r="D13" s="13" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="13"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="23"/>
+      <c r="B14" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C14" s="13"/>
+      <c r="D14" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="E14" s="13"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="23"/>
+      <c r="B15" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="D15" s="13"/>
+      <c r="E15" s="13"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="23"/>
+      <c r="B16" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C16" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="D16" s="13"/>
+      <c r="E16" s="13"/>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="23"/>
+      <c r="B17" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="C17" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="23"/>
+      <c r="B18" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="23"/>
+      <c r="B19" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>200</v>
+      </c>
+      <c r="D19" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="E19" s="13"/>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="23"/>
+      <c r="B20" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>210</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A3:A12"/>
+    <mergeCell ref="A13:A20"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:E1"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>